--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.6026855674735</v>
+        <v>5.785436404714444</v>
       </c>
       <c r="D2" t="n">
-        <v>35.4363404734791</v>
+        <v>5.758405326940354</v>
       </c>
       <c r="E2" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F2" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.84032966784156</v>
+        <v>3.549053571024253</v>
       </c>
       <c r="D3" t="n">
-        <v>21.27204738618265</v>
+        <v>3.456707700254681</v>
       </c>
       <c r="E3" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F3" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.39242115692471</v>
+        <v>2.176268438000266</v>
       </c>
       <c r="D4" t="n">
-        <v>37.19560433913772</v>
+        <v>6.04428570510988</v>
       </c>
       <c r="E4" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F4" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.22126282127281</v>
+        <v>3.123455208456832</v>
       </c>
       <c r="D5" t="n">
-        <v>39.80062216250571</v>
+        <v>6.467601101407178</v>
       </c>
       <c r="E5" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F5" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.39886963580756</v>
+        <v>3.802316315818728</v>
       </c>
       <c r="D6" t="n">
-        <v>18.8676805539782</v>
+        <v>3.065998090021457</v>
       </c>
       <c r="E6" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F6" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.54689600559404</v>
+        <v>4.151370600909032</v>
       </c>
       <c r="D7" t="n">
-        <v>8.796669356773354</v>
+        <v>1.42945877047567</v>
       </c>
       <c r="E7" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F7" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.680512859033422</v>
+        <v>1.248083339592931</v>
       </c>
       <c r="D8" t="n">
-        <v>27.73348225399224</v>
+        <v>4.506690866273739</v>
       </c>
       <c r="E8" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F8" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.97034749875734</v>
+        <v>2.595181468548069</v>
       </c>
       <c r="D9" t="n">
-        <v>15.46343570061467</v>
+        <v>2.512808301349884</v>
       </c>
       <c r="E9" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F9" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.88473427625861</v>
+        <v>4.043769319892024</v>
       </c>
       <c r="D10" t="n">
-        <v>22.83830933185672</v>
+        <v>3.711225266426718</v>
       </c>
       <c r="E10" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F10" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.41029983097621</v>
+        <v>4.616673722533634</v>
       </c>
       <c r="D11" t="n">
-        <v>33.85696999280381</v>
+        <v>5.50175762383062</v>
       </c>
       <c r="E11" t="n">
-        <v>7.553701929894089</v>
+        <v>1.22747656360779</v>
       </c>
       <c r="F11" t="n">
-        <v>9.795992611287252</v>
+        <v>1.591848799334179</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
